--- a/rawresource/rawconfig/item.xlsx
+++ b/rawresource/rawconfig/item.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="29">
   <si>
     <t>item_conf</t>
   </si>
@@ -106,6 +106,15 @@
   </si>
   <si>
     <t>sell</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>元宝</t>
+  </si>
+  <si>
+    <t>经验</t>
   </si>
   <si>
     <t>这是一把短剑</t>
@@ -1321,7 +1330,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="8.99074074074074" defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="13.8796296296296" customWidth="1"/>
@@ -1447,81 +1456,123 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
       <c r="D6">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>55</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="B7">
-        <v>10001</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>10001</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>85</v>
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="B8">
-        <v>20000</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>20000</v>
+        <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8">
-        <v>99</v>
-      </c>
-      <c r="G8">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9">
+        <v>10000</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9">
+        <v>10000</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10">
+        <v>10001</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10">
+        <v>10001</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11">
+        <v>20000</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11">
+        <v>20000</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11">
+        <v>99</v>
+      </c>
+      <c r="G11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12">
         <v>20001</v>
       </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9">
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12">
         <v>20001</v>
       </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9">
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12">
         <v>99</v>
       </c>
-      <c r="G9">
+      <c r="G12">
         <v>18</v>
       </c>
     </row>

--- a/rawresource/rawconfig/item.xlsx
+++ b/rawresource/rawconfig/item.xlsx
@@ -34,7 +34,7 @@
     <author xml:space="preserve"> </author>
   </authors>
   <commentList>
-    <comment ref="G2" authorId="0">
+    <comment ref="I2" authorId="0">
       <text>
         <r>
           <rPr>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="33">
   <si>
     <t>item_conf</t>
   </si>
@@ -66,6 +66,12 @@
     <t>唯一id</t>
   </si>
   <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>背包类型id</t>
+  </si>
+  <si>
     <t>描述</t>
   </si>
   <si>
@@ -91,6 +97,12 @@
   </si>
   <si>
     <t>id</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>bag_id</t>
   </si>
   <si>
     <t>desc</t>
@@ -1330,15 +1342,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultColWidth="8.99074074074074" defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="13.8796296296296" customWidth="1"/>
-    <col min="4" max="4" width="7.5" customWidth="1"/>
-    <col min="7" max="7" width="14.75" customWidth="1"/>
+    <col min="5" max="5" width="13.8796296296296" customWidth="1"/>
+    <col min="6" max="6" width="7.5" customWidth="1"/>
+    <col min="9" max="9" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -1347,18 +1359,20 @@
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="1"/>
+      <c r="I1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
       <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:12">
       <c r="A2" s="1"/>
       <c r="B2" s="3" t="s">
         <v>3</v>
@@ -1372,207 +1386,264 @@
       <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:12">
       <c r="A3" s="1"/>
       <c r="B3" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:12">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:12">
       <c r="A5" s="1"/>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+      <c r="F5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:12">
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6">
+      <c r="C6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:12">
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7">
+      <c r="C7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:12">
       <c r="B8">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8">
+      <c r="C8">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:12">
       <c r="B9">
         <v>10000</v>
       </c>
-      <c r="C9" t="s">
-        <v>21</v>
+      <c r="C9">
+        <v>1000</v>
       </c>
       <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9">
         <v>10000</v>
       </c>
-      <c r="E9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9">
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9">
         <v>1</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:12">
       <c r="B10">
         <v>10001</v>
       </c>
-      <c r="C10" t="s">
-        <v>23</v>
+      <c r="C10">
+        <v>1000</v>
       </c>
       <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10">
         <v>10001</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10">
+      <c r="G10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10">
         <v>1</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:12">
       <c r="B11">
         <v>20000</v>
       </c>
-      <c r="C11" t="s">
-        <v>25</v>
+      <c r="C11">
+        <v>1000</v>
       </c>
       <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11">
         <v>20000</v>
       </c>
-      <c r="E11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11">
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11">
         <v>99</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:12">
       <c r="B12">
         <v>20001</v>
       </c>
-      <c r="C12" t="s">
-        <v>27</v>
+      <c r="C12">
+        <v>1000</v>
       </c>
       <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12">
         <v>20001</v>
       </c>
-      <c r="E12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12">
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12">
         <v>99</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>18</v>
       </c>
     </row>
